--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484248_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484248_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9295</v>
+        <v>6.8205</v>
       </c>
       <c r="E2" t="n">
         <v>4.0672</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8623</v>
+        <v>2.7534</v>
       </c>
       <c r="G2" t="n">
         <v>4.3193</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7004</v>
+        <v>0.5915</v>
       </c>
       <c r="T2" t="n">
         <v>0.2504</v>
       </c>
       <c r="U2" t="n">
-        <v>0.45</v>
+        <v>0.341</v>
       </c>
       <c r="V2" t="n">
         <v>2.1052</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3671</v>
+        <v>6.3011</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1795</v>
+        <v>3.705</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1875</v>
+        <v>2.5961</v>
       </c>
       <c r="G3" t="n">
         <v>3.6998</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4815</v>
+        <v>0.4526</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0689</v>
+        <v>0.5944</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5503</v>
+        <v>-0.1418</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4227</v>
+        <v>4.7232</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4723</v>
+        <v>3.004</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9504</v>
+        <v>1.7192</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7176</v>
+        <v>4.6698</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9069</v>
+        <v>4.306</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1893</v>
+        <v>0.3638</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4544</v>
+        <v>4.6995</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0476</v>
+        <v>4.6048</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2632</v>
+        <v>-0.0297</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8593</v>
+        <v>-0.2988</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4039</v>
+        <v>0.269</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q4" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0808</v>
+        <v>0.7882</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1517</v>
+        <v>0.7154</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9291</v>
+        <v>0.0727</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7731</v>
+        <v>1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7731</v>
+        <v>1.4959</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2683</v>
+        <v>3.3471</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1951</v>
+        <v>3.1557</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0733</v>
+        <v>0.1914</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6698</v>
+        <v>-0.1235</v>
       </c>
       <c r="H5" t="n">
-        <v>4.306</v>
+        <v>0.7667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3638</v>
+        <v>-0.8902</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6995</v>
+        <v>1.1198</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6048</v>
+        <v>1.0655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0543</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0297</v>
+        <v>-1.2433</v>
       </c>
       <c r="N5" t="n">
         <v>-0.2988</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269</v>
+        <v>-0.9445</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3333</v>
+        <v>1.6659</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0935</v>
+        <v>1.794</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4268</v>
+        <v>-0.128</v>
       </c>
       <c r="V5" t="n">
         <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6869</v>
+        <v>2.5696</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9041</v>
+        <v>-0.7816</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2171</v>
+        <v>3.3512</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1235</v>
+        <v>1.7176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7667</v>
+        <v>1.9069</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8902</v>
+        <v>-0.1893</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1198</v>
+        <v>0.4544</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0655</v>
+        <v>1.0476</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0543</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2433</v>
+        <v>1.2632</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2988</v>
+        <v>0.8593</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9445</v>
+        <v>0.4039</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0058</v>
+        <v>1.2277</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5424</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5366</v>
+        <v>0.3299</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1549</v>
+        <v>2.4338</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8998</v>
+        <v>1.1514</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2552</v>
+        <v>1.2824</v>
       </c>
       <c r="G7" t="n">
         <v>1.607</v>
@@ -1000,13 +1000,13 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7433</v>
+        <v>1.0221</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6592</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1113</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9587</v>
+        <v>1.2141</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6743</v>
+        <v>2.2293</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7156</v>
+        <v>-1.0152</v>
       </c>
       <c r="G8" t="n">
         <v>0.7252</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3589</v>
+        <v>1.6143</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8683</v>
+        <v>1.4232</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4906</v>
+        <v>0.1911</v>
       </c>
       <c r="V8" t="n">
         <v>1.2186</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2739</v>
+        <v>0.9535</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0801</v>
+        <v>0.4346</v>
       </c>
       <c r="F9" t="n">
-        <v>0.354</v>
+        <v>0.5188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5802</v>
+        <v>2.8692</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1758</v>
+        <v>1.0893</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4045</v>
+        <v>1.7799</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0409</v>
+        <v>3.3688</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0409</v>
+        <v>0.779</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.5898</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5393</v>
+        <v>-0.4996</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1348</v>
+        <v>0.3103</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4045</v>
+        <v>-0.8099</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1425</v>
+        <v>0.2097</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>0.6955</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0215</v>
+        <v>-0.4858</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5545</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. SIMON RAMIS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5685</v>
+        <v>0.1922</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0605</v>
+        <v>-0.0801</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.508</v>
+        <v>0.2723</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1998</v>
+        <v>0.5802</v>
       </c>
       <c r="H10" t="n">
-        <v>0.065</v>
+        <v>0.1758</v>
       </c>
       <c r="I10" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.1348</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.1998</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.065</v>
-      </c>
       <c r="O10" t="n">
-        <v>0.1348</v>
+        <v>0.4045</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.159</v>
+        <v>-0.2242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0605</v>
+        <v>-0.121</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0985</v>
+        <v>-0.1032</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>N. SIMON RAMIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5951</v>
+        <v>-0.413</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5964</v>
+        <v>0.0406</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0014</v>
+        <v>-0.4535</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8692</v>
+        <v>0.1998</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0893</v>
+        <v>0.065</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7799</v>
+        <v>0.1348</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3688</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5898</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4996</v>
+        <v>0.1998</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3103</v>
+        <v>0.065</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8099</v>
+        <v>0.1348</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3388</v>
+        <v>-0.0034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3356</v>
+        <v>0.0406</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0032</v>
+        <v>-0.044</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6093</v>
+        <v>-0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3321</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3958</v>
+        <v>-0.5379</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2479</v>
+        <v>-1.5807</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8522</v>
+        <v>1.0428</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0346</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3379</v>
+        <v>0.52</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4237</v>
+        <v>0.2436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0858</v>
+        <v>0.2764</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5979</v>
+        <v>-3.0941</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9031</v>
+        <v>-3.2359</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3051</v>
+        <v>0.1417</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6527</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0548</v>
+        <v>1.5586</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4596</v>
+        <v>1.1268</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5952</v>
+        <v>0.4318</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6093</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.9047</v>
+        <v>24.5101</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5043</v>
+        <v>12.1095</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4007</v>
+        <v>12.4006</v>
       </c>
       <c r="G14" t="n">
         <v>14.5771</v>
@@ -1516,7 +1516,7 @@
         <v>13.23</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3473</v>
+        <v>1.347299999999999</v>
       </c>
       <c r="J14" t="n">
         <v>15.4766</v>
@@ -1525,10 +1525,10 @@
         <v>12.1002</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3763</v>
+        <v>3.376299999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8995000000000006</v>
+        <v>-0.8995000000000004</v>
       </c>
       <c r="N14" t="n">
         <v>1.1295</v>
@@ -1537,7 +1537,7 @@
         <v>-2.0292</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.860199999999999</v>
+        <v>-5.8602</v>
       </c>
       <c r="Q14" t="n">
         <v>-22.4645</v>
@@ -1546,13 +1546,13 @@
         <v>16.6042</v>
       </c>
       <c r="S14" t="n">
-        <v>8.817599999999999</v>
+        <v>9.423</v>
       </c>
       <c r="T14" t="n">
-        <v>7.9662</v>
+        <v>8.571400000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8514999999999998</v>
+        <v>0.8514</v>
       </c>
       <c r="V14" t="n">
         <v>6.370299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2252</v>
+        <v>1.2963</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2803</v>
+        <v>1.3814</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0551</v>
+        <v>-0.0851</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1732</v>
@@ -1624,13 +1624,13 @@
         <v>3.7115</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3951</v>
+        <v>-0.3239</v>
       </c>
       <c r="T15" t="n">
-        <v>0.091</v>
+        <v>0.1921</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4861</v>
+        <v>-0.516</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9414</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1619</v>
+        <v>0.1142</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0936</v>
+        <v>1.3969</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2554</v>
+        <v>-1.2827</v>
       </c>
       <c r="G16" t="n">
         <v>2.0049</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7528</v>
+        <v>-0.4767</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2888</v>
+        <v>0.0145</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4639</v>
+        <v>-0.4912</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.122</v>
+        <v>-0.6437</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8778</v>
+        <v>-1.3723</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7558</v>
+        <v>0.7286</v>
       </c>
       <c r="G17" t="n">
         <v>-0.901</v>
@@ -1780,13 +1780,13 @@
         <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3345</v>
+        <v>0.1438</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3494</v>
+        <v>0.1562</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0148</v>
+        <v>-0.0124</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2772</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1233</v>
+        <v>-1.5742</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0555</v>
+        <v>-1.4599</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1788</v>
+        <v>-0.1143</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9436</v>
+        <v>-1.3863</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1341</v>
+        <v>-1.0629</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8095</v>
+        <v>-0.3233</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6351</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7704</v>
+        <v>-0.5692</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1352</v>
+        <v>-0.0533</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3085</v>
+        <v>-0.7638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3638</v>
+        <v>-0.4937</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9447</v>
+        <v>-0.27</v>
       </c>
       <c r="P18" t="n">
         <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5581</v>
+        <v>-0.4539</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6208</v>
+        <v>-0.1732</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0627</v>
+        <v>-0.2807</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8865</v>
+        <v>-1.8828</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0466</v>
+        <v>-0.6642</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.9331</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8983</v>
+        <v>-2.2227</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4599</v>
+        <v>0.741</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4384</v>
+        <v>-2.9636</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3863</v>
+        <v>-2.9436</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0629</v>
+        <v>-2.1341</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3233</v>
+        <v>-0.8095</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-1.6351</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5692</v>
+        <v>-1.7704</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0533</v>
+        <v>0.1352</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7638</v>
+        <v>-1.3085</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4937</v>
+        <v>-0.3638</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.27</v>
+        <v>-0.9447</v>
       </c>
       <c r="P19" t="n">
         <v>2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>3.1255</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.778</v>
+        <v>-0.5413</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1732</v>
+        <v>0.3063</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6048</v>
+        <v>-0.8475</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8828</v>
+        <v>-0.8865</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>3.0466</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-3.9331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7098</v>
+        <v>-2.5826</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6713</v>
+        <v>-0.3464</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0384</v>
+        <v>-2.2362</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4287</v>
+        <v>-1.3131</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9455</v>
+        <v>-0.1264</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4832</v>
+        <v>-1.1867</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8229</v>
+        <v>1.0138</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3901</v>
+        <v>0.9862</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.213</v>
+        <v>0.0276</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6059</v>
+        <v>-2.3269</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.3356</v>
+        <v>-1.1125</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2702</v>
+        <v>-1.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3748</v>
+        <v>-2.1178</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1282</v>
+        <v>-1.0282</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7534</v>
+        <v>-1.0896</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2101</v>
+        <v>-3.3631</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6498</v>
+        <v>-1.3792</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5603</v>
+        <v>-1.984</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3131</v>
+        <v>-3.4287</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1264</v>
+        <v>-1.9455</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1867</v>
+        <v>-1.4832</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0138</v>
+        <v>-0.8229</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9862</v>
+        <v>0.3901</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0276</v>
+        <v>-1.213</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3269</v>
+        <v>-2.6059</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1125</v>
+        <v>-2.3356</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2144</v>
+        <v>-0.2702</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7452</v>
+        <v>-0.2785</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3315</v>
+        <v>0.4204</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4137</v>
+        <v>-0.6989</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1638</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8977</v>
+        <v>-3.9443</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4565</v>
+        <v>-2.5576</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4412</v>
+        <v>-1.3867</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0238</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8386</v>
+        <v>-0.8852</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0246</v>
+        <v>-0.1257</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8139</v>
+        <v>-0.7595</v>
       </c>
       <c r="V22" t="n">
         <v>1.5507</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2906</v>
+        <v>-4.2447</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.058</v>
+        <v>-3.6453</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2326</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6812</v>
+        <v>1.2688</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.144</v>
+        <v>-0.7017</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5371</v>
+        <v>1.9706</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1872</v>
+        <v>4.7638</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2459</v>
+        <v>1.8483</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9414</v>
+        <v>2.9155</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4939</v>
+        <v>-3.4949</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8982</v>
+        <v>-2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4043</v>
+        <v>-0.9449</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9767</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-7.8137</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>4.1022</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6328</v>
+        <v>-1.802</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.5954</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7154</v>
+        <v>-1.2066</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7161</v>
+        <v>-5.3918</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6565</v>
+        <v>-5.1591</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0596</v>
+        <v>-0.2326</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2688</v>
+        <v>-3.6812</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7017</v>
+        <v>-2.144</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9706</v>
+        <v>-1.5371</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7638</v>
+        <v>-3.1872</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8483</v>
+        <v>-1.2459</v>
       </c>
       <c r="L24" t="n">
-        <v>2.9155</v>
+        <v>-1.9414</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.4949</v>
+        <v>-0.4939</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.55</v>
+        <v>-0.8982</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9449</v>
+        <v>0.4043</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.7115</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.8137</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>4.1022</v>
+        <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.2734</v>
+        <v>-0.7339</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6066</v>
+        <v>-0.0185</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6669</v>
+        <v>-0.7154</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.9046</v>
+        <v>-22.5566</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.4004</v>
+        <v>-12.4005</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.504</v>
+        <v>-10.1559</v>
       </c>
       <c r="G25" t="n">
         <v>-14.5772</v>
@@ -2377,13 +2377,13 @@
         <v>-1.3471</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8994999999999997</v>
+        <v>0.8995000000000006</v>
       </c>
       <c r="K25" t="n">
         <v>-1.1297</v>
       </c>
       <c r="L25" t="n">
-        <v>2.0291</v>
+        <v>2.029100000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-15.4766</v>
@@ -2395,7 +2395,7 @@
         <v>-3.3763</v>
       </c>
       <c r="P25" t="n">
-        <v>5.860400000000001</v>
+        <v>5.8604</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.604</v>
@@ -2404,13 +2404,13 @@
         <v>22.4645</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.817500000000001</v>
+        <v>-7.4694</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8514999999999997</v>
+        <v>-0.8515</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.966</v>
+        <v>-6.6178</v>
       </c>
       <c r="V25" t="n">
         <v>-6.3703</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484248_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484248_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7232</v>
+        <v>3.3471</v>
       </c>
       <c r="E4" t="n">
-        <v>3.004</v>
+        <v>3.1557</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7192</v>
+        <v>0.1914</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6698</v>
+        <v>-0.1235</v>
       </c>
       <c r="H4" t="n">
-        <v>4.306</v>
+        <v>0.7667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3638</v>
+        <v>-0.8902</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6995</v>
+        <v>1.1198</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6048</v>
+        <v>1.0655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0543</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0297</v>
+        <v>-1.2433</v>
       </c>
       <c r="N4" t="n">
         <v>-0.2988</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>-0.9445</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7882</v>
+        <v>1.6659</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7154</v>
+        <v>1.794</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0727</v>
+        <v>-0.128</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3471</v>
+        <v>2.5813</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1557</v>
+        <v>0.8621</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1914</v>
+        <v>1.7192</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1235</v>
+        <v>2.5279</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7667</v>
+        <v>2.7711</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8902</v>
+        <v>-0.2432</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1198</v>
+        <v>2.5576</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0655</v>
+        <v>3.0699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0543</v>
+        <v>-0.5122</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2433</v>
+        <v>-0.0297</v>
       </c>
       <c r="N5" t="n">
         <v>-0.2988</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9445</v>
+        <v>0.269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6659</v>
+        <v>0.7882</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794</v>
+        <v>0.7154</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.128</v>
+        <v>0.0727</v>
       </c>
       <c r="V5" t="n">
         <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2141</v>
+        <v>2.1419</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2293</v>
+        <v>2.1419</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0152</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7252</v>
+        <v>2.1419</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9729</v>
+        <v>1.5349</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6982</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0337</v>
+        <v>2.1419</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6092</v>
+        <v>1.5349</v>
       </c>
       <c r="L8" t="n">
-        <v>3.6429</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3085</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3638</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9447</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6143</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4232</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1911</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9535</v>
+        <v>1.2141</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4346</v>
+        <v>2.2293</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5188</v>
+        <v>-1.0152</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8692</v>
+        <v>0.7252</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0893</v>
+        <v>-1.9729</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7799</v>
+        <v>2.6982</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3688</v>
+        <v>2.0337</v>
       </c>
       <c r="K9" t="n">
-        <v>0.779</v>
+        <v>-1.6092</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5898</v>
+        <v>3.6429</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4996</v>
+        <v>-1.3085</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3103</v>
+        <v>-0.3638</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8099</v>
+        <v>-0.9447</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7348</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2097</v>
+        <v>1.6143</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6955</v>
+        <v>1.4232</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4858</v>
+        <v>0.1911</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>3.6559</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3321</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1922</v>
+        <v>0.9535</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0801</v>
+        <v>0.4346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2723</v>
+        <v>0.5188</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5802</v>
+        <v>2.8692</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1758</v>
+        <v>1.0893</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4045</v>
+        <v>1.7799</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0409</v>
+        <v>3.3688</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0409</v>
+        <v>0.779</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.5898</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5393</v>
+        <v>-0.4996</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1348</v>
+        <v>0.3103</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4045</v>
+        <v>-0.8099</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2242</v>
+        <v>0.2097</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>0.6955</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1032</v>
+        <v>-0.4858</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. SIMON RAMIS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.413</v>
+        <v>0.1922</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0406</v>
+        <v>-0.0801</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4535</v>
+        <v>0.2723</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1998</v>
+        <v>0.5802</v>
       </c>
       <c r="H11" t="n">
-        <v>0.065</v>
+        <v>0.1758</v>
       </c>
       <c r="I11" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.1348</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1998</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.065</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.1348</v>
+        <v>0.4045</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0034</v>
+        <v>-0.2242</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0406</v>
+        <v>-0.121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.044</v>
+        <v>-0.1032</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>N. SIMON RAMIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5379</v>
+        <v>-0.413</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5807</v>
+        <v>0.0406</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0428</v>
+        <v>-0.4535</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0346</v>
+        <v>0.1998</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5646</v>
+        <v>0.065</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.47</v>
+        <v>0.1348</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8243</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.164</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6603</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2103</v>
+        <v>0.1998</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5994</v>
+        <v>0.065</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8097</v>
+        <v>0.1348</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.52</v>
+        <v>-0.0034</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2436</v>
+        <v>0.0406</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2764</v>
+        <v>-0.044</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0941</v>
+        <v>-0.5379</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2359</v>
+        <v>-1.5807</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1417</v>
+        <v>1.0428</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6527</v>
+        <v>-2.0346</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8698</v>
+        <v>-0.5646</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7829</v>
+        <v>-1.47</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4092</v>
+        <v>-1.8243</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.5711</v>
+        <v>-1.164</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1619</v>
+        <v>-0.6603</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2435</v>
+        <v>-0.2103</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2988</v>
+        <v>0.5994</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9447</v>
+        <v>-0.8097</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5586</v>
+        <v>0.52</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1268</v>
+        <v>0.2436</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4318</v>
+        <v>0.2764</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.5101</v>
+        <v>-3.0941</v>
       </c>
       <c r="E14" t="n">
-        <v>12.1095</v>
+        <v>-3.2359</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4006</v>
+        <v>0.1417</v>
       </c>
       <c r="G14" t="n">
-        <v>14.5771</v>
+        <v>-3.6527</v>
       </c>
       <c r="H14" t="n">
-        <v>13.23</v>
+        <v>-2.8698</v>
       </c>
       <c r="I14" t="n">
-        <v>1.347299999999999</v>
+        <v>-0.7829</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4766</v>
+        <v>-2.4092</v>
       </c>
       <c r="K14" t="n">
-        <v>12.1002</v>
+        <v>-2.5711</v>
       </c>
       <c r="L14" t="n">
-        <v>3.376299999999999</v>
+        <v>0.1619</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8995000000000004</v>
+        <v>-1.2435</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1295</v>
+        <v>-0.2988</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0292</v>
+        <v>-0.9447</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.8602</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.4645</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>16.6042</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>9.423</v>
+        <v>1.5586</v>
       </c>
       <c r="T14" t="n">
-        <v>8.571400000000001</v>
+        <v>1.1268</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8514</v>
+        <v>0.4318</v>
       </c>
       <c r="V14" t="n">
-        <v>6.370299999999999</v>
+        <v>-0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>10.5259</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.1555</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2963</v>
+        <v>24.5101</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3814</v>
+        <v>12.1095</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0851</v>
+        <v>12.4006</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1732</v>
+        <v>14.5771</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0089</v>
+        <v>13.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8358</v>
+        <v>1.3473</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8887</v>
+        <v>15.4766</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5129</v>
+        <v>12.1002</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3758</v>
+        <v>3.376400000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0619</v>
+        <v>-0.8995000000000002</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5219</v>
+        <v>1.1295</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5401</v>
+        <v>-2.0292</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7348</v>
+        <v>-5.8602</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-22.4645</v>
       </c>
       <c r="R15" t="n">
-        <v>3.7115</v>
+        <v>16.6042</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3239</v>
+        <v>9.423</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1921</v>
+        <v>8.571400000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.516</v>
+        <v>0.8514000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9414</v>
+        <v>6.370299999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>10.5259</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-4.1555</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1142</v>
+        <v>1.2963</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3969</v>
+        <v>1.3814</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2827</v>
+        <v>-0.0851</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0049</v>
+        <v>-0.1732</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4405</v>
+        <v>-1.0089</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5643</v>
+        <v>0.8358</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3591</v>
+        <v>1.8887</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0642</v>
+        <v>0.5129</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2949</v>
+        <v>1.3758</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3542</v>
+        <v>-2.0619</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6237</v>
+        <v>-1.5219</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>-0.5401</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>2.7348</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>3.7115</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4767</v>
+        <v>-0.3239</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0145</v>
+        <v>0.1921</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4912</v>
+        <v>-0.516</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>-0.9414</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6437</v>
+        <v>0.1142</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3723</v>
+        <v>1.3969</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7286</v>
+        <v>-1.2827</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.901</v>
+        <v>2.0049</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6718</v>
+        <v>0.4405</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2292</v>
+        <v>1.5643</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5518</v>
+        <v>2.3591</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0819</v>
+        <v>1.0642</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.2949</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3492</v>
+        <v>-0.3542</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7536</v>
+        <v>-0.6237</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4045</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1438</v>
+        <v>-0.4767</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1562</v>
+        <v>0.0145</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0124</v>
+        <v>-0.4912</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5742</v>
+        <v>-0.6437</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4599</v>
+        <v>-1.3723</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1143</v>
+        <v>0.7286</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3863</v>
+        <v>-0.901</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0629</v>
+        <v>-0.6718</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3233</v>
+        <v>-0.2292</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.5518</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5692</v>
+        <v>0.0819</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0533</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7638</v>
+        <v>-0.3492</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4937</v>
+        <v>-0.7536</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.27</v>
+        <v>0.4045</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4539</v>
+        <v>0.1438</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1732</v>
+        <v>0.1562</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2807</v>
+        <v>-0.0124</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8828</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2227</v>
+        <v>-1.5742</v>
       </c>
       <c r="E19" t="n">
-        <v>0.741</v>
+        <v>-1.4599</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9636</v>
+        <v>-0.1143</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9436</v>
+        <v>-1.3863</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1341</v>
+        <v>-1.0629</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8095</v>
+        <v>-0.3233</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6351</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7704</v>
+        <v>-0.5692</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1352</v>
+        <v>-0.0533</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3085</v>
+        <v>-0.7638</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3638</v>
+        <v>-0.4937</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9447</v>
+        <v>-0.27</v>
       </c>
       <c r="P19" t="n">
         <v>2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5413</v>
+        <v>-0.4539</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3063</v>
+        <v>-0.1732</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8475</v>
+        <v>-0.2807</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>-1.8828</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0466</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.9331</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5826</v>
+        <v>-2.2227</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3464</v>
+        <v>0.741</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2362</v>
+        <v>-2.9636</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3131</v>
+        <v>-2.9436</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1264</v>
+        <v>-2.1341</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1867</v>
+        <v>-0.8095</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0138</v>
+        <v>-1.6351</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9862</v>
+        <v>-1.7704</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0276</v>
+        <v>0.1352</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3269</v>
+        <v>-1.3085</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1125</v>
+        <v>-0.3638</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2144</v>
+        <v>-0.9447</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1178</v>
+        <v>-0.5413</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0282</v>
+        <v>0.3063</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0896</v>
+        <v>-0.8475</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>3.0466</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1638</v>
+        <v>-3.9331</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3631</v>
+        <v>-2.5826</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3792</v>
+        <v>-0.3464</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.984</v>
+        <v>-2.2362</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4287</v>
+        <v>-1.3131</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9455</v>
+        <v>-0.1264</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4832</v>
+        <v>-1.1867</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8229</v>
+        <v>1.0138</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3901</v>
+        <v>0.9862</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.213</v>
+        <v>0.0276</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6059</v>
+        <v>-2.3269</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3356</v>
+        <v>-1.1125</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2702</v>
+        <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2785</v>
+        <v>-2.1178</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4204</v>
+        <v>-1.0282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6989</v>
+        <v>-1.0896</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9443</v>
+        <v>-3.3631</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5576</v>
+        <v>-1.3792</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3867</v>
+        <v>-1.984</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0238</v>
+        <v>-3.4287</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.875</v>
+        <v>-1.9455</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1488</v>
+        <v>-1.4832</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3064</v>
+        <v>-0.8229</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.4278</v>
+        <v>0.3901</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>-1.213</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7174</v>
+        <v>-2.6059</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4472</v>
+        <v>-2.3356</v>
       </c>
       <c r="O22" t="n">
         <v>-0.2702</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8852</v>
+        <v>-0.2785</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1257</v>
+        <v>0.4204</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7595</v>
+        <v>-0.6989</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5507</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2447</v>
+        <v>-3.9443</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6453</v>
+        <v>-2.5576</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-1.3867</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2688</v>
+        <v>-4.0238</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7017</v>
+        <v>-3.875</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9706</v>
+        <v>-0.1488</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7638</v>
+        <v>-2.3064</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8483</v>
+        <v>-2.4278</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9155</v>
+        <v>0.1214</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.4949</v>
+        <v>-1.7174</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.55</v>
+        <v>-1.4472</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9449</v>
+        <v>-0.2702</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.7115</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.8137</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>4.1022</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.802</v>
+        <v>-0.8852</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5954</v>
+        <v>-0.1257</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2066</v>
+        <v>-0.7595</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.5507</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3918</v>
+        <v>-4.2447</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1591</v>
+        <v>-3.6453</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2326</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6812</v>
+        <v>1.2688</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.144</v>
+        <v>-0.7017</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5371</v>
+        <v>1.9706</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1872</v>
+        <v>4.7638</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2459</v>
+        <v>1.8483</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9414</v>
+        <v>2.9155</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4939</v>
+        <v>-3.4949</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8982</v>
+        <v>-2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4043</v>
+        <v>-0.9449</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9767</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-7.8137</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9767</v>
+        <v>4.1022</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7339</v>
+        <v>-1.802</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0185</v>
+        <v>-0.5954</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7154</v>
+        <v>-1.2066</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2342,12 +2453,17 @@
       </c>
       <c r="X24" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-5.3918</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.1591</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.2326</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.6812</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.144</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.5371</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.1872</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.2459</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.9414</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.4939</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8982</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7339</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.7154</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484248_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-22.5566</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-12.4005</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-10.1559</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-14.5772</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>-13.2298</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-1.3471</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>0.8995000000000006</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>-1.1297</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>2.029100000000001</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-15.4766</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-12.1002</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-3.3763</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>5.8604</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>22.4645</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-7.4694</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-0.8515</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>-6.6178</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-6.3703</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>4.1554</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-10.5257</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
